--- a/QCM4_SVT.xlsx
+++ b/QCM4_SVT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE56DAA9-83CF-43CB-895C-BD90927427A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823BB7B3-71FB-48B4-A1B4-36CB6E741176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="112">
   <si>
     <t>Question</t>
   </si>
@@ -354,8 +354,15 @@
     <t>L'isolement des gènes de l'insuline en utilisant des enzymes restrictases</t>
   </si>
   <si>
-    <t>Lorsque vous réalisez dans votre laboratoire l'expérience décrite sur le document 1 (méduse fluorescente vers drosophile) :
-&lt;img src="/images/SVT_QCM4_Q5.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+    <t>Image</t>
+  </si>
+  <si>
+    <t>SVT_QCM4_Q5.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lorsque vous réalisez dans votre laboratoire l'expérience décrite sur le document 1 (méduse fluorescente vers drosophile) :
+&lt;img src="/images/SVT_QCM4_Q5.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+</t>
   </si>
 </sst>
 </file>
@@ -438,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -450,6 +457,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -754,18 +764,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="30.42578125" customWidth="1"/>
     <col min="4" max="7" width="35" customWidth="1"/>
-    <col min="8" max="8" width="33.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" customWidth="1"/>
+    <col min="8" max="9" width="33.140625" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -791,10 +801,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -819,8 +832,9 @@
       <c r="H2" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -845,8 +859,9 @@
       <c r="H3" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -871,8 +886,9 @@
       <c r="H4" s="4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -897,13 +913,14 @@
       <c r="H5" s="4" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -923,8 +940,11 @@
       <c r="H6" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -949,8 +969,9 @@
       <c r="H7" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -975,8 +996,9 @@
       <c r="H8" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1001,8 +1023,9 @@
       <c r="H9" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -1027,8 +1050,9 @@
       <c r="H10" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1053,8 +1077,9 @@
       <c r="H11" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -1079,8 +1104,9 @@
       <c r="H12" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -1105,8 +1131,9 @@
       <c r="H13" s="4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1131,8 +1158,9 @@
       <c r="H14" s="4" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1157,8 +1185,9 @@
       <c r="H15" s="4" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
@@ -1183,8 +1212,9 @@
       <c r="H16" s="4" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>10</v>
       </c>
@@ -1209,8 +1239,9 @@
       <c r="H17" s="4" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>10</v>
       </c>
@@ -1235,8 +1266,9 @@
       <c r="H18" s="4" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>10</v>
       </c>
@@ -1261,8 +1293,9 @@
       <c r="H19" s="4" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -1287,8 +1320,9 @@
       <c r="H20" s="4" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -1313,6 +1347,7 @@
       <c r="H21" s="4" t="s">
         <v>108</v>
       </c>
+      <c r="I21" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/QCM4_SVT.xlsx
+++ b/QCM4_SVT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823BB7B3-71FB-48B4-A1B4-36CB6E741176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84B67CE-25A6-40A6-AA5E-14A224F6835B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -360,8 +360,7 @@
     <t>SVT_QCM4_Q5.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Lorsque vous réalisez dans votre laboratoire l'expérience décrite sur le document 1 (méduse fluorescente vers drosophile) :
-&lt;img src="/images/SVT_QCM4_Q5.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+    <t xml:space="preserve">Lorsque vous réalisez dans votre laboratoire l'expérience décrite sur le document 1 &lt;img src="/images/SVT_QCM4_Q5.png" alt="A"class="h-20 block ml-auto my-1" /&gt; (méduse fluorescente vers drosophile) :
 </t>
   </si>
 </sst>

--- a/QCM4_SVT.xlsx
+++ b/QCM4_SVT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84B67CE-25A6-40A6-AA5E-14A224F6835B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F320602D-053C-43CB-A1DA-0A402F5E62A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,9 +57,6 @@
     <t>Explication</t>
   </si>
   <si>
-    <t>QCM Chapitre 4</t>
-  </si>
-  <si>
     <t>En génie génétique, le transfert du gène d'une hormone humaine (insuline ou hormone de croissance) dans une bactérie nécessite :</t>
   </si>
   <si>
@@ -362,6 +359,9 @@
   <si>
     <t xml:space="preserve">Lorsque vous réalisez dans votre laboratoire l'expérience décrite sur le document 1 &lt;img src="/images/SVT_QCM4_Q5.png" alt="A"class="h-20 block ml-auto my-1" /&gt; (méduse fluorescente vers drosophile) :
 </t>
+  </si>
+  <si>
+    <t>TEST : Le génie génétique</t>
   </si>
 </sst>
 </file>
@@ -800,7 +800,7 @@
         <v>8</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>9</v>
@@ -808,543 +808,543 @@
     </row>
     <row r="2" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="H3" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H4" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:10" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="H5" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="H6" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="H7" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="H8" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="H9" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>64</v>
-      </c>
       <c r="H10" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>68</v>
-      </c>
       <c r="H11" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>72</v>
-      </c>
       <c r="H12" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>76</v>
-      </c>
       <c r="H13" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I13" s="5"/>
     </row>
     <row r="14" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="H14" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="H15" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="H16" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="F17" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>92</v>
-      </c>
       <c r="H17" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="H18" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>100</v>
-      </c>
       <c r="H19" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>104</v>
-      </c>
       <c r="H20" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="F21" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="G21" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>108</v>
-      </c>
       <c r="H21" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I21" s="5"/>
     </row>
